--- a/Avançado2-Excel/planilha_vendas 2.xlsx
+++ b/Avançado2-Excel/planilha_vendas 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu.sharepoint.com/sites/Section_sec_276219900361495/Documentos Compartilhados/General/YuriMendes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuri.smendes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="13_ncr:1_{6EC5A9B8-2545-4284-BE56-1761E7DD0174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31FEC6CF-E770-4E68-B626-13A4618EA313}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B2A33-ABC5-4543-967A-0E6ECCAEA2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,7 +213,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +223,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,7 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -299,6 +305,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -315,10 +322,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1491,6 +1494,12 @@
         <v>20</v>
       </c>
     </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H3" s="11" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(H4)</f>
+        <v>=FILTRO(A5:F34;(A5:A34=$A$2)*(C5:C34=$B$2)*(D5:D34=$C$2);"N/A")</v>
+      </c>
+    </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
@@ -2172,6 +2181,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004338EACDEB32E14E811804BCC8CF8A06" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="f7e76c7d54f00e2f0aff52ac894d7b1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b9ab6d4d-6490-4164-9fc0-592559187bb4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e30e541039ea0fb7b0c185bae0535c77" ns2:_="">
     <xsd:import namespace="b9ab6d4d-6490-4164-9fc0-592559187bb4"/>
@@ -2309,35 +2333,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{906D8064-0869-4405-B327-E3C3E690876E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB732FED-B829-4E84-B5AB-D80E164F4BC5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b9ab6d4d-6490-4164-9fc0-592559187bb4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2359,9 +2358,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB732FED-B829-4E84-B5AB-D80E164F4BC5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{906D8064-0869-4405-B327-E3C3E690876E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b9ab6d4d-6490-4164-9fc0-592559187bb4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>